--- a/output/yearly_total_coral_cover_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_17_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248956294669788</v>
+        <v>1.2793119336851</v>
       </c>
       <c r="C3" t="n">
-        <v>4.633345418532828</v>
+        <v>4.674755536697958</v>
       </c>
       <c r="D3" t="n">
-        <v>6.012934801827686</v>
+        <v>6.040247022959831</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8952365150303</v>
+        <v>11.99431449334289</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.366745937643064</v>
+        <v>1.441066839595151</v>
       </c>
       <c r="C4" t="n">
-        <v>5.140906390728936</v>
+        <v>5.280009401119411</v>
       </c>
       <c r="D4" t="n">
-        <v>6.327842235980449</v>
+        <v>6.301814100315751</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83549456435245</v>
+        <v>13.02289034103031</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.527396331255847</v>
+        <v>1.664628835389479</v>
       </c>
       <c r="C5" t="n">
-        <v>5.787634280868474</v>
+        <v>6.047794393135161</v>
       </c>
       <c r="D5" t="n">
-        <v>6.716309272078481</v>
+        <v>6.582033857134479</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0313398842028</v>
+        <v>14.29445708565912</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.71274982407755</v>
+        <v>1.920425859083441</v>
       </c>
       <c r="C6" t="n">
-        <v>6.616972786452509</v>
+        <v>7.021561952518119</v>
       </c>
       <c r="D6" t="n">
-        <v>7.122080663746829</v>
+        <v>6.873559219722188</v>
       </c>
       <c r="E6" t="n">
-        <v>15.45180327427689</v>
+        <v>15.81554703132375</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.917912885520251</v>
+        <v>2.199580927334705</v>
       </c>
       <c r="C7" t="n">
-        <v>7.62167549932996</v>
+        <v>8.12122404939814</v>
       </c>
       <c r="D7" t="n">
-        <v>7.487373675000455</v>
+        <v>7.273377591149871</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02696205985067</v>
+        <v>17.59418256788272</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.136775275564108</v>
+        <v>1.387878260128655</v>
       </c>
       <c r="C8" t="n">
-        <v>5.356143537561466</v>
+        <v>5.711279109467705</v>
       </c>
       <c r="D8" t="n">
-        <v>5.777192383915543</v>
+        <v>5.514919369714385</v>
       </c>
       <c r="E8" t="n">
-        <v>12.27011119704112</v>
+        <v>12.61407673931074</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.394531673285419</v>
+        <v>1.74288253896624</v>
       </c>
       <c r="C9" t="n">
-        <v>6.694063749178095</v>
+        <v>7.004016726618723</v>
       </c>
       <c r="D9" t="n">
-        <v>6.28872581111718</v>
+        <v>5.978886894699467</v>
       </c>
       <c r="E9" t="n">
-        <v>14.37732123358069</v>
+        <v>14.72578616028443</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.663068024220914</v>
+        <v>2.106360595629797</v>
       </c>
       <c r="C10" t="n">
-        <v>8.247125708728188</v>
+        <v>8.493032583913084</v>
       </c>
       <c r="D10" t="n">
-        <v>6.795458489959432</v>
+        <v>6.455715070732437</v>
       </c>
       <c r="E10" t="n">
-        <v>16.70565222290853</v>
+        <v>17.05510825027532</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.931509347579435</v>
+        <v>2.473505014738259</v>
       </c>
       <c r="C11" t="n">
-        <v>9.948217463113069</v>
+        <v>10.13280548981655</v>
       </c>
       <c r="D11" t="n">
-        <v>7.361820881559962</v>
+        <v>6.974346999811846</v>
       </c>
       <c r="E11" t="n">
-        <v>19.24154769225247</v>
+        <v>19.58065750436666</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.193047967513691</v>
+        <v>2.834465601245295</v>
       </c>
       <c r="C12" t="n">
-        <v>11.80209261861386</v>
+        <v>11.85177415592928</v>
       </c>
       <c r="D12" t="n">
-        <v>7.825877040087509</v>
+        <v>7.386437369187565</v>
       </c>
       <c r="E12" t="n">
-        <v>21.82101762621506</v>
+        <v>22.07267712636214</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.42823505490548</v>
+        <v>3.172852189248662</v>
       </c>
       <c r="C13" t="n">
-        <v>13.66600056956273</v>
+        <v>13.64390692283358</v>
       </c>
       <c r="D13" t="n">
-        <v>8.294996089244403</v>
+        <v>7.826567190277953</v>
       </c>
       <c r="E13" t="n">
-        <v>24.38923171371261</v>
+        <v>24.6433263023602</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.409475544033061</v>
+        <v>1.830841658695792</v>
       </c>
       <c r="C14" t="n">
-        <v>9.521146315418246</v>
+        <v>9.616375842730188</v>
       </c>
       <c r="D14" t="n">
-        <v>6.286915948455725</v>
+        <v>5.969134034068075</v>
       </c>
       <c r="E14" t="n">
-        <v>17.21753780790703</v>
+        <v>17.41635153549406</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.404164288953085</v>
+        <v>1.861167845279976</v>
       </c>
       <c r="C15" t="n">
-        <v>10.48298417622293</v>
+        <v>10.4799014884316</v>
       </c>
       <c r="D15" t="n">
-        <v>6.29544733600563</v>
+        <v>5.948212990490576</v>
       </c>
       <c r="E15" t="n">
-        <v>18.18259580118165</v>
+        <v>18.28928232420215</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.586131225935232</v>
+        <v>2.139080985398163</v>
       </c>
       <c r="C16" t="n">
-        <v>12.53248068360857</v>
+        <v>12.41975641220696</v>
       </c>
       <c r="D16" t="n">
-        <v>6.751832391278843</v>
+        <v>6.403066519345165</v>
       </c>
       <c r="E16" t="n">
-        <v>20.87044430082265</v>
+        <v>20.96190391695028</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.242941680961674</v>
+        <v>1.698914402199105</v>
       </c>
       <c r="C17" t="n">
-        <v>11.6745117299132</v>
+        <v>11.4219767679498</v>
       </c>
       <c r="D17" t="n">
-        <v>6.254498639261495</v>
+        <v>5.927458844022798</v>
       </c>
       <c r="E17" t="n">
-        <v>19.17195205013637</v>
+        <v>19.0483500141717</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.391048139624348</v>
+        <v>1.926130090869988</v>
       </c>
       <c r="C18" t="n">
-        <v>13.72566739091902</v>
+        <v>13.31297992596183</v>
       </c>
       <c r="D18" t="n">
-        <v>6.627179885270627</v>
+        <v>6.306550902540661</v>
       </c>
       <c r="E18" t="n">
-        <v>21.74389541581399</v>
+        <v>21.54566091937248</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.371403368062369</v>
+        <v>1.923911341058389</v>
       </c>
       <c r="C19" t="n">
-        <v>14.75952626330725</v>
+        <v>14.19743643271778</v>
       </c>
       <c r="D19" t="n">
-        <v>6.688519481831967</v>
+        <v>6.369422025520627</v>
       </c>
       <c r="E19" t="n">
-        <v>22.81944911320159</v>
+        <v>22.4907697992968</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.495211571044935</v>
+        <v>2.130019454087965</v>
       </c>
       <c r="C20" t="n">
-        <v>17.00274122769487</v>
+        <v>16.23633006489756</v>
       </c>
       <c r="D20" t="n">
-        <v>7.08709923227913</v>
+        <v>6.72397039143232</v>
       </c>
       <c r="E20" t="n">
-        <v>25.58505203101894</v>
+        <v>25.09031991041784</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.8766810649383169</v>
+        <v>1.263175501146201</v>
       </c>
       <c r="C21" t="n">
-        <v>12.47790532872949</v>
+        <v>11.85884467886258</v>
       </c>
       <c r="D21" t="n">
-        <v>5.889425937960276</v>
+        <v>5.59337991774465</v>
       </c>
       <c r="E21" t="n">
-        <v>19.24401233162808</v>
+        <v>18.71540009775343</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_17_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.2793119336851</v>
+        <v>1.252794928193393</v>
       </c>
       <c r="C3" t="n">
-        <v>4.674755536697958</v>
+        <v>4.63653609857163</v>
       </c>
       <c r="D3" t="n">
-        <v>6.040247022959831</v>
+        <v>6.06693092556126</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99431449334289</v>
+        <v>11.95626195232628</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.441066839595151</v>
+        <v>1.374451974072519</v>
       </c>
       <c r="C4" t="n">
-        <v>5.280009401119411</v>
+        <v>5.143561041051052</v>
       </c>
       <c r="D4" t="n">
-        <v>6.301814100315751</v>
+        <v>6.410729959294016</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02289034103031</v>
+        <v>12.92874297441759</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.664628835389479</v>
+        <v>1.551340841160279</v>
       </c>
       <c r="C5" t="n">
-        <v>6.047794393135161</v>
+        <v>5.787772542786939</v>
       </c>
       <c r="D5" t="n">
-        <v>6.582033857134479</v>
+        <v>6.809156702781245</v>
       </c>
       <c r="E5" t="n">
-        <v>14.29445708565912</v>
+        <v>14.14827008672846</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.920425859083441</v>
+        <v>1.7650906731271</v>
       </c>
       <c r="C6" t="n">
-        <v>7.021561952518119</v>
+        <v>6.562287575396178</v>
       </c>
       <c r="D6" t="n">
-        <v>6.873559219722188</v>
+        <v>7.308948834292481</v>
       </c>
       <c r="E6" t="n">
-        <v>15.81554703132375</v>
+        <v>15.63632708281576</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.199580927334705</v>
+        <v>2.005447609966355</v>
       </c>
       <c r="C7" t="n">
-        <v>8.12122404939814</v>
+        <v>7.446709962867407</v>
       </c>
       <c r="D7" t="n">
-        <v>7.273377591149871</v>
+        <v>7.840339320734555</v>
       </c>
       <c r="E7" t="n">
-        <v>17.59418256788272</v>
+        <v>17.29249689356832</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.387878260128655</v>
+        <v>1.239625010879656</v>
       </c>
       <c r="C8" t="n">
-        <v>5.711279109467705</v>
+        <v>5.036049731295354</v>
       </c>
       <c r="D8" t="n">
-        <v>5.514919369714385</v>
+        <v>6.176840964710271</v>
       </c>
       <c r="E8" t="n">
-        <v>12.61407673931074</v>
+        <v>12.45251570688528</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.74288253896624</v>
+        <v>1.550790397762938</v>
       </c>
       <c r="C9" t="n">
-        <v>7.004016726618723</v>
+        <v>6.146817682615733</v>
       </c>
       <c r="D9" t="n">
-        <v>5.978886894699467</v>
+        <v>6.930011349008041</v>
       </c>
       <c r="E9" t="n">
-        <v>14.72578616028443</v>
+        <v>14.62761942938671</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.106360595629797</v>
+        <v>1.858672057243206</v>
       </c>
       <c r="C10" t="n">
-        <v>8.493032583913084</v>
+        <v>7.398721048750422</v>
       </c>
       <c r="D10" t="n">
-        <v>6.455715070732437</v>
+        <v>7.639747678432779</v>
       </c>
       <c r="E10" t="n">
-        <v>17.05510825027532</v>
+        <v>16.89714078442641</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.473505014738259</v>
+        <v>2.172384260811813</v>
       </c>
       <c r="C11" t="n">
-        <v>10.13280548981655</v>
+        <v>8.780618497000152</v>
       </c>
       <c r="D11" t="n">
-        <v>6.974346999811846</v>
+        <v>8.471434610892027</v>
       </c>
       <c r="E11" t="n">
-        <v>19.58065750436666</v>
+        <v>19.42443736870399</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.834465601245295</v>
+        <v>2.470693253387365</v>
       </c>
       <c r="C12" t="n">
-        <v>11.85177415592928</v>
+        <v>10.25567285272847</v>
       </c>
       <c r="D12" t="n">
-        <v>7.386437369187565</v>
+        <v>9.234507566452629</v>
       </c>
       <c r="E12" t="n">
-        <v>22.07267712636214</v>
+        <v>21.96087367256847</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.172852189248662</v>
+        <v>2.75329668619319</v>
       </c>
       <c r="C13" t="n">
-        <v>13.64390692283358</v>
+        <v>11.71728369697371</v>
       </c>
       <c r="D13" t="n">
-        <v>7.826567190277953</v>
+        <v>9.973419044806013</v>
       </c>
       <c r="E13" t="n">
-        <v>24.6433263023602</v>
+        <v>24.44399942797292</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.830841658695792</v>
+        <v>1.587220965886946</v>
       </c>
       <c r="C14" t="n">
-        <v>9.616375842730188</v>
+        <v>8.239877204082777</v>
       </c>
       <c r="D14" t="n">
-        <v>5.969134034068075</v>
+        <v>7.604087573335499</v>
       </c>
       <c r="E14" t="n">
-        <v>17.41635153549406</v>
+        <v>17.43118574330522</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.861167845279976</v>
+        <v>1.603684874887165</v>
       </c>
       <c r="C15" t="n">
-        <v>10.4799014884316</v>
+        <v>8.851388214104031</v>
       </c>
       <c r="D15" t="n">
-        <v>5.948212990490576</v>
+        <v>7.786987170636682</v>
       </c>
       <c r="E15" t="n">
-        <v>18.28928232420215</v>
+        <v>18.24206025962788</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.139080985398163</v>
+        <v>1.833178218231899</v>
       </c>
       <c r="C16" t="n">
-        <v>12.41975641220696</v>
+        <v>10.37661181246779</v>
       </c>
       <c r="D16" t="n">
-        <v>6.403066519345165</v>
+        <v>8.52067668245145</v>
       </c>
       <c r="E16" t="n">
-        <v>20.96190391695028</v>
+        <v>20.73046671315114</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.698914402199105</v>
+        <v>1.453987984943611</v>
       </c>
       <c r="C17" t="n">
-        <v>11.4219767679498</v>
+        <v>9.510504170304213</v>
       </c>
       <c r="D17" t="n">
-        <v>5.927458844022798</v>
+        <v>8.082552134477226</v>
       </c>
       <c r="E17" t="n">
-        <v>19.0483500141717</v>
+        <v>19.04704428972505</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.926130090869988</v>
+        <v>1.637250828895363</v>
       </c>
       <c r="C18" t="n">
-        <v>13.31297992596183</v>
+        <v>11.03620882504305</v>
       </c>
       <c r="D18" t="n">
-        <v>6.306550902540661</v>
+        <v>8.68949801767373</v>
       </c>
       <c r="E18" t="n">
-        <v>21.54566091937248</v>
+        <v>21.36295767161215</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.923911341058389</v>
+        <v>1.627698423733042</v>
       </c>
       <c r="C19" t="n">
-        <v>14.19743643271778</v>
+        <v>11.74517792966489</v>
       </c>
       <c r="D19" t="n">
-        <v>6.369422025520627</v>
+        <v>8.896136274463601</v>
       </c>
       <c r="E19" t="n">
-        <v>22.4907697992968</v>
+        <v>22.26901262786153</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.130019454087965</v>
+        <v>1.794615168409085</v>
       </c>
       <c r="C20" t="n">
-        <v>16.23633006489756</v>
+        <v>13.4077087619446</v>
       </c>
       <c r="D20" t="n">
-        <v>6.72397039143232</v>
+        <v>9.499488961062562</v>
       </c>
       <c r="E20" t="n">
-        <v>25.09031991041784</v>
+        <v>24.70181289141625</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.263175501146201</v>
+        <v>1.058166945545382</v>
       </c>
       <c r="C21" t="n">
-        <v>11.85884467886258</v>
+        <v>9.824368911351916</v>
       </c>
       <c r="D21" t="n">
-        <v>5.59337991774465</v>
+        <v>8.010472218031424</v>
       </c>
       <c r="E21" t="n">
-        <v>18.71540009775343</v>
+        <v>18.89300807492872</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_17_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252794928193393</v>
+        <v>2.604046037490024</v>
       </c>
       <c r="C3" t="n">
-        <v>4.63653609857163</v>
+        <v>7.768390038474751</v>
       </c>
       <c r="D3" t="n">
-        <v>6.06693092556126</v>
+        <v>8.201793015692465</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95626195232628</v>
+        <v>18.57422909165724</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.374451974072519</v>
+        <v>1.100599712670781</v>
       </c>
       <c r="C4" t="n">
-        <v>5.143561041051052</v>
+        <v>4.641926195429222</v>
       </c>
       <c r="D4" t="n">
-        <v>6.410729959294016</v>
+        <v>5.794323492107941</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92874297441759</v>
+        <v>11.53684940020794</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.551340841160279</v>
+        <v>1.211980735608281</v>
       </c>
       <c r="C5" t="n">
-        <v>5.787772542786939</v>
+        <v>5.445581062725798</v>
       </c>
       <c r="D5" t="n">
-        <v>6.809156702781245</v>
+        <v>6.145404344194524</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14827008672846</v>
+        <v>12.8029661425286</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.7650906731271</v>
+        <v>1.328123521785214</v>
       </c>
       <c r="C6" t="n">
-        <v>6.562287575396178</v>
+        <v>6.506101165720239</v>
       </c>
       <c r="D6" t="n">
-        <v>7.308948834292481</v>
+        <v>6.481669414706692</v>
       </c>
       <c r="E6" t="n">
-        <v>15.63632708281576</v>
+        <v>14.31589410221214</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.005447609966355</v>
+        <v>1.445259583523081</v>
       </c>
       <c r="C7" t="n">
-        <v>7.446709962867407</v>
+        <v>7.77296365261776</v>
       </c>
       <c r="D7" t="n">
-        <v>7.840339320734555</v>
+        <v>6.922410915032828</v>
       </c>
       <c r="E7" t="n">
-        <v>17.29249689356832</v>
+        <v>16.14063415117367</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.239625010879656</v>
+        <v>1.563500960343379</v>
       </c>
       <c r="C8" t="n">
-        <v>5.036049731295354</v>
+        <v>9.21010405477162</v>
       </c>
       <c r="D8" t="n">
-        <v>6.176840964710271</v>
+        <v>7.352399123514766</v>
       </c>
       <c r="E8" t="n">
-        <v>12.45251570688528</v>
+        <v>18.12600413862976</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.550790397762938</v>
+        <v>1.665573679857584</v>
       </c>
       <c r="C9" t="n">
-        <v>6.146817682615733</v>
+        <v>10.81652740843633</v>
       </c>
       <c r="D9" t="n">
-        <v>6.930011349008041</v>
+        <v>7.725850624758529</v>
       </c>
       <c r="E9" t="n">
-        <v>14.62761942938671</v>
+        <v>20.20795171305245</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.858672057243206</v>
+        <v>1.041703036545163</v>
       </c>
       <c r="C10" t="n">
-        <v>7.398721048750422</v>
+        <v>7.829202321919294</v>
       </c>
       <c r="D10" t="n">
-        <v>7.639747678432779</v>
+        <v>6.07981627024486</v>
       </c>
       <c r="E10" t="n">
-        <v>16.89714078442641</v>
+        <v>14.95072162870932</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.172384260811813</v>
+        <v>0.9578028777402308</v>
       </c>
       <c r="C11" t="n">
-        <v>8.780618497000152</v>
+        <v>8.57684246861141</v>
       </c>
       <c r="D11" t="n">
-        <v>8.471434610892027</v>
+        <v>5.932986083597707</v>
       </c>
       <c r="E11" t="n">
-        <v>19.42443736870399</v>
+        <v>15.46763142994935</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.470693253387365</v>
+        <v>1.011671374272253</v>
       </c>
       <c r="C12" t="n">
-        <v>10.25567285272847</v>
+        <v>10.31876723773357</v>
       </c>
       <c r="D12" t="n">
-        <v>9.234507566452629</v>
+        <v>6.320177560675607</v>
       </c>
       <c r="E12" t="n">
-        <v>21.96087367256847</v>
+        <v>17.65061617268143</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.75329668619319</v>
+        <v>0.7864289984869075</v>
       </c>
       <c r="C13" t="n">
-        <v>11.71728369697371</v>
+        <v>9.930584195474379</v>
       </c>
       <c r="D13" t="n">
-        <v>9.973419044806013</v>
+        <v>5.75901057292813</v>
       </c>
       <c r="E13" t="n">
-        <v>24.44399942797292</v>
+        <v>16.47602376688942</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.587220965886946</v>
+        <v>0.8335921581989243</v>
       </c>
       <c r="C14" t="n">
-        <v>8.239877204082777</v>
+        <v>11.74602223269054</v>
       </c>
       <c r="D14" t="n">
-        <v>7.604087573335499</v>
+        <v>6.111271466688927</v>
       </c>
       <c r="E14" t="n">
-        <v>17.43118574330522</v>
+        <v>18.69088585757839</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.603684874887165</v>
+        <v>0.7910137602657402</v>
       </c>
       <c r="C15" t="n">
-        <v>8.851388214104031</v>
+        <v>12.77239037009537</v>
       </c>
       <c r="D15" t="n">
-        <v>7.786987170636682</v>
+        <v>6.141715462997621</v>
       </c>
       <c r="E15" t="n">
-        <v>18.24206025962788</v>
+        <v>19.70511959335873</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.833178218231899</v>
+        <v>0.8477980474793756</v>
       </c>
       <c r="C16" t="n">
-        <v>10.37661181246779</v>
+        <v>14.87632478768149</v>
       </c>
       <c r="D16" t="n">
-        <v>8.52067668245145</v>
+        <v>6.536476214875264</v>
       </c>
       <c r="E16" t="n">
-        <v>20.73046671315114</v>
+        <v>22.26059905003613</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.453987984943611</v>
+        <v>0.5008582262755953</v>
       </c>
       <c r="C17" t="n">
-        <v>9.510504170304213</v>
+        <v>11.07510566908531</v>
       </c>
       <c r="D17" t="n">
-        <v>8.082552134477226</v>
+        <v>5.426011569124654</v>
       </c>
       <c r="E17" t="n">
-        <v>19.04704428972505</v>
+        <v>17.00197546448556</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.637250828895363</v>
+        <v>0.3798774566812609</v>
       </c>
       <c r="C18" t="n">
-        <v>11.03620882504305</v>
+        <v>10.01744923234614</v>
       </c>
       <c r="D18" t="n">
-        <v>8.68949801767373</v>
+        <v>4.928000411191374</v>
       </c>
       <c r="E18" t="n">
-        <v>21.36295767161215</v>
+        <v>15.32532710021877</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.627698423733042</v>
+        <v>0.434305549404704</v>
       </c>
       <c r="C19" t="n">
-        <v>11.74517792966489</v>
+        <v>12.35547157253287</v>
       </c>
       <c r="D19" t="n">
-        <v>8.896136274463601</v>
+        <v>5.431234466911247</v>
       </c>
       <c r="E19" t="n">
-        <v>22.26901262786153</v>
+        <v>18.22101158884882</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.794615168409085</v>
+        <v>0.4863479952068274</v>
       </c>
       <c r="C20" t="n">
-        <v>13.4077087619446</v>
+        <v>14.85942890969141</v>
       </c>
       <c r="D20" t="n">
-        <v>9.499488961062562</v>
+        <v>5.863105282009419</v>
       </c>
       <c r="E20" t="n">
-        <v>24.70181289141625</v>
+        <v>21.20888218690765</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.058166945545382</v>
+        <v>0.5305560943290613</v>
       </c>
       <c r="C21" t="n">
-        <v>9.824368911351916</v>
+        <v>17.33784117158543</v>
       </c>
       <c r="D21" t="n">
-        <v>8.010472218031424</v>
+        <v>6.261753754795878</v>
       </c>
       <c r="E21" t="n">
-        <v>18.89300807492872</v>
+        <v>24.13015102071038</v>
       </c>
     </row>
   </sheetData>
